--- a/backtest_runs/20260410_193731/by_symbol/UVIC/UVIC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/UVIC/UVIC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-9044.549999999992</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>90955.45000000001</v>
@@ -817,7 +817,7 @@
         <v>-5363.099999999999</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>90319.15000000001</v>
@@ -863,7 +863,7 @@
         <v>-5999.400000000001</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>84319.75</v>
@@ -1139,7 +1139,7 @@
         <v>-6681.149999999995</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>91137.25</v>
@@ -1323,7 +1323,7 @@
         <v>-10089.89999999999</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>87455.80000000002</v>
@@ -1553,7 +1553,7 @@
         <v>-2363.399999999998</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>95682.25</v>
